--- a/forms/trg/Formulir_TRG_idlfrg.xlsx
+++ b/forms/trg/Formulir_TRG_idlfrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,37 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Jasmal Ahmari Syamsu</t>
+          <t>Prof. Sitti Nurani Sirajuddin</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Feed Industry</t>
-        </is>
-      </c>
+          <t>Livestock Institutions</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1410-5201</t>
+          <t>0000-0002-3875-3185</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57208472974</t>
+          <t>55969235700</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Budiman</t>
+          <t>Prof. Jasmal Ahmari Syamsu</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,18 +969,22 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Forage Crops</t>
+          <t>Feed Industry</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1410-5201</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>58662068600</t>
+          <t>57208472974</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Muhammad Arsyad</t>
+          <t>Prof. Budiman</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,22 +1014,18 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Institutions</t>
+          <t>Forage Crops</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-5619-4543</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57202770024</t>
+          <t>58662068600</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,22 +1040,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Emely J. Escala</t>
+          <t>Prof. Muhammad Arsyad</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Capiz State University, Philipine</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Animal Nutrition</t>
+          <t>Agricultural Institutions</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,11 +1064,15 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2666-9901</t>
+          <t>0000-0001-5619-4543</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57202770024</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1085,29 +1085,33 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Mohd Azid Kabul, Ph.D</t>
+          <t>Emely J. Escala</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Wholly owned by Sawit Kinabalu Group</t>
+          <t>Capiz State University, Philipine</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Consultant (Integrated Cattle-Oil Palm System), Malaysia</t>
+          <t>Animal Nutrition</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-2666-9901</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1122,39 +1126,31 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Abdel Razzaq Mohammad Al-Tawaha, Ph.D</t>
+          <t>Mohd Azid Kabul, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>National Agricultural Research Center (NARC), Jordan</t>
+          <t>Wholly owned by Sawit Kinabalu Group</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Plant production</t>
+          <t>Consultant (Integrated Cattle-Oil Palm System), Malaysia</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0826-0942%20</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57217942115</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1167,22 +1163,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Alwi Akbar</t>
+          <t>Abdel Razzaq Mohammad Al-Tawaha, Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>National Agricultural Research Center (NARC), Jordan</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Feasibility Study</t>
+          <t>Plant production</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1191,13 +1187,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-5922-3145</t>
+          <t>0000-0003-0826-0942%20</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>58710506100</t>
+          <t>57217942115</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1212,12 +1208,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Mutmainnah Aras</t>
+          <t>Muhammad Alwi Akbar</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1227,16 +1223,24 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Agribusines</t>
+          <t>Feasibility Study</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0009-0003-5922-3145</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>58710506100</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1249,22 +1253,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Putri Alya Ariqa Ali</t>
+          <t>Mutmainnah Aras</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
           <t>Agribusines</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>IDLF-RG Team</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1284,10 +1288,26 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Putri Alya Ariqa Ali</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Agribusines</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>IDLF-RG Team</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1295,7 +1315,11 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1484,15 +1508,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
